--- a/outputs/Wage_(non-qualified_labour,_agricultural)_tukey_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_agricultural)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="90">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>Minimal</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Alarm</t>
@@ -841,7 +844,7 @@
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
         <v>79</v>
@@ -853,7 +856,7 @@
         <v>79</v>
       </c>
       <c r="J2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K2" t="s">
         <v>79</v>
@@ -886,7 +889,7 @@
         <v>79</v>
       </c>
       <c r="U2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -901,88 +904,88 @@
         <v>79</v>
       </c>
       <c r="Z2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -990,64 +993,64 @@
         <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R3" t="s">
         <v>79</v>
       </c>
       <c r="S3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T3" t="s">
         <v>79</v>
       </c>
       <c r="U3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1056,94 +1059,94 @@
         <v>79</v>
       </c>
       <c r="X3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="s">
         <v>79</v>
       </c>
       <c r="AC3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1157,19 +1160,19 @@
         <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s">
         <v>79</v>
@@ -1196,10 +1199,10 @@
         <v>79</v>
       </c>
       <c r="Q4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S4" t="s">
         <v>79</v>
@@ -1217,25 +1220,25 @@
         <v>79</v>
       </c>
       <c r="X4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="s">
         <v>79</v>
       </c>
       <c r="AB4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC4" t="s">
         <v>79</v>
       </c>
       <c r="AD4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE4" t="s">
         <v>79</v>
@@ -1253,7 +1256,7 @@
         <v>79</v>
       </c>
       <c r="AJ4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK4" t="s">
         <v>79</v>
@@ -1271,7 +1274,7 @@
         <v>79</v>
       </c>
       <c r="AP4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ4" t="s">
         <v>79</v>
@@ -1298,13 +1301,13 @@
         <v>79</v>
       </c>
       <c r="AY4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1312,70 +1315,70 @@
         <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S5" t="s">
         <v>79</v>
       </c>
       <c r="T5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X5" t="s">
         <v>79</v>
@@ -1390,13 +1393,13 @@
         <v>79</v>
       </c>
       <c r="AB5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC5" t="s">
         <v>79</v>
       </c>
       <c r="AD5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1405,7 +1408,7 @@
         <v>79</v>
       </c>
       <c r="AG5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s">
         <v>79</v>
@@ -1414,7 +1417,7 @@
         <v>79</v>
       </c>
       <c r="AJ5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="s">
         <v>79</v>
@@ -1426,7 +1429,7 @@
         <v>79</v>
       </c>
       <c r="AN5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO5" t="s">
         <v>79</v>
@@ -1441,7 +1444,7 @@
         <v>79</v>
       </c>
       <c r="AS5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT5" t="s">
         <v>79</v>
@@ -1453,19 +1456,19 @@
         <v>79</v>
       </c>
       <c r="AW5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX5" t="s">
         <v>79</v>
       </c>
       <c r="AY5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1473,55 +1476,55 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S6" t="s">
         <v>79</v>
@@ -1530,28 +1533,28 @@
         <v>79</v>
       </c>
       <c r="U6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W6" t="s">
         <v>79</v>
       </c>
       <c r="X6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC6" t="s">
         <v>79</v>
@@ -1566,13 +1569,13 @@
         <v>79</v>
       </c>
       <c r="AG6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="s">
         <v>79</v>
@@ -1584,34 +1587,34 @@
         <v>79</v>
       </c>
       <c r="AM6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR6" t="s">
         <v>79</v>
       </c>
       <c r="AS6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT6" t="s">
         <v>79</v>
       </c>
       <c r="AU6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW6" t="s">
         <v>79</v>
@@ -1620,13 +1623,13 @@
         <v>79</v>
       </c>
       <c r="AY6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="BA6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1634,121 +1637,121 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO7" t="s">
         <v>79</v>
@@ -1757,37 +1760,37 @@
         <v>79</v>
       </c>
       <c r="AQ7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1795,55 +1798,55 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S8" t="s">
         <v>79</v>
@@ -1855,7 +1858,7 @@
         <v>79</v>
       </c>
       <c r="V8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W8" t="s">
         <v>79</v>
@@ -1864,10 +1867,10 @@
         <v>79</v>
       </c>
       <c r="Y8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA8" t="s">
         <v>79</v>
@@ -1879,22 +1882,22 @@
         <v>79</v>
       </c>
       <c r="AD8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF8" t="s">
         <v>79</v>
       </c>
       <c r="AG8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH8" t="s">
         <v>79</v>
       </c>
       <c r="AI8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="s">
         <v>79</v>
@@ -1906,13 +1909,13 @@
         <v>79</v>
       </c>
       <c r="AM8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP8" t="s">
         <v>79</v>
@@ -1924,31 +1927,31 @@
         <v>79</v>
       </c>
       <c r="AS8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -1956,49 +1959,49 @@
         <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="s">
         <v>79</v>
@@ -2019,7 +2022,7 @@
         <v>79</v>
       </c>
       <c r="W9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X9" t="s">
         <v>79</v>
@@ -2031,7 +2034,7 @@
         <v>79</v>
       </c>
       <c r="AA9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB9" t="s">
         <v>79</v>
@@ -2061,10 +2064,10 @@
         <v>79</v>
       </c>
       <c r="AK9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="s">
         <v>79</v>
@@ -2073,10 +2076,10 @@
         <v>79</v>
       </c>
       <c r="AO9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ9" t="s">
         <v>79</v>
@@ -2088,28 +2091,28 @@
         <v>79</v>
       </c>
       <c r="AT9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2117,55 +2120,55 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S10" t="s">
         <v>79</v>
@@ -2174,7 +2177,7 @@
         <v>79</v>
       </c>
       <c r="U10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -2183,13 +2186,13 @@
         <v>79</v>
       </c>
       <c r="X10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y10" t="s">
         <v>79</v>
       </c>
       <c r="Z10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA10" t="s">
         <v>79</v>
@@ -2198,79 +2201,79 @@
         <v>79</v>
       </c>
       <c r="AC10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK10" t="s">
         <v>79</v>
       </c>
       <c r="AL10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2278,121 +2281,121 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="s">
         <v>79</v>
@@ -2404,34 +2407,34 @@
         <v>79</v>
       </c>
       <c r="AR11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2439,142 +2442,142 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="s">
         <v>79</v>
       </c>
       <c r="AP12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT12" t="s">
         <v>79</v>
       </c>
       <c r="AU12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV12" t="s">
         <v>79</v>
@@ -2583,16 +2586,16 @@
         <v>79</v>
       </c>
       <c r="AX12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2600,19 +2603,19 @@
         <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
         <v>79</v>
@@ -2624,94 +2627,94 @@
         <v>79</v>
       </c>
       <c r="J13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="s">
         <v>79</v>
       </c>
       <c r="AM13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="s">
         <v>79</v>
@@ -2732,7 +2735,7 @@
         <v>79</v>
       </c>
       <c r="AT13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU13" t="s">
         <v>79</v>
@@ -2741,19 +2744,19 @@
         <v>79</v>
       </c>
       <c r="AW13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2761,55 +2764,55 @@
         <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S14" t="s">
         <v>79</v>
@@ -2830,7 +2833,7 @@
         <v>79</v>
       </c>
       <c r="Y14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z14" t="s">
         <v>79</v>
@@ -2845,28 +2848,28 @@
         <v>79</v>
       </c>
       <c r="AD14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL14" t="s">
         <v>79</v>
@@ -2884,7 +2887,7 @@
         <v>79</v>
       </c>
       <c r="AQ14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR14" t="s">
         <v>79</v>
@@ -2893,10 +2896,10 @@
         <v>79</v>
       </c>
       <c r="AT14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV14" t="s">
         <v>79</v>
@@ -2905,16 +2908,16 @@
         <v>79</v>
       </c>
       <c r="AX14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -2922,109 +2925,109 @@
         <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="s">
         <v>79</v>
@@ -3039,10 +3042,10 @@
         <v>79</v>
       </c>
       <c r="AO15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ15" t="s">
         <v>79</v>
@@ -3054,28 +3057,28 @@
         <v>79</v>
       </c>
       <c r="AT15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3083,115 +3086,115 @@
         <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="s">
         <v>79</v>
@@ -3212,7 +3215,7 @@
         <v>79</v>
       </c>
       <c r="AS16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT16" t="s">
         <v>79</v>
@@ -3230,13 +3233,13 @@
         <v>79</v>
       </c>
       <c r="AY16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3244,28 +3247,28 @@
         <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s">
         <v>79</v>
       </c>
       <c r="H17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J17" t="s">
         <v>79</v>
@@ -3274,13 +3277,13 @@
         <v>79</v>
       </c>
       <c r="L17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M17" t="s">
         <v>79</v>
       </c>
       <c r="N17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O17" t="s">
         <v>79</v>
@@ -3292,7 +3295,7 @@
         <v>79</v>
       </c>
       <c r="R17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S17" t="s">
         <v>79</v>
@@ -3328,7 +3331,7 @@
         <v>79</v>
       </c>
       <c r="AD17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE17" t="s">
         <v>79</v>
@@ -3355,49 +3358,49 @@
         <v>79</v>
       </c>
       <c r="AM17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AN17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AO17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AP17" t="s">
         <v>79</v>
       </c>
       <c r="AQ17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AR17" t="s">
         <v>79</v>
       </c>
       <c r="AS17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT17" t="s">
         <v>81</v>
       </c>
-      <c r="AT17" t="s">
-        <v>80</v>
-      </c>
       <c r="AU17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AW17" t="s">
         <v>79</v>
       </c>
       <c r="AX17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3408,7 +3411,7 @@
         <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>79</v>
@@ -3420,31 +3423,31 @@
         <v>79</v>
       </c>
       <c r="G18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s">
         <v>79</v>
       </c>
       <c r="I18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P18" t="s">
         <v>79</v>
@@ -3462,34 +3465,34 @@
         <v>79</v>
       </c>
       <c r="U18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
       </c>
       <c r="W18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y18" t="s">
         <v>79</v>
       </c>
       <c r="Z18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="s">
         <v>79</v>
       </c>
       <c r="AC18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE18" t="s">
         <v>79</v>
@@ -3510,7 +3513,7 @@
         <v>79</v>
       </c>
       <c r="AK18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL18" t="s">
         <v>79</v>
@@ -3519,46 +3522,46 @@
         <v>79</v>
       </c>
       <c r="AN18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AR18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AZ18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3575,7 +3578,7 @@
         <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
         <v>79</v>
@@ -3587,13 +3590,13 @@
         <v>79</v>
       </c>
       <c r="I19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J19" t="s">
         <v>79</v>
       </c>
       <c r="K19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L19" t="s">
         <v>79</v>
@@ -3611,7 +3614,7 @@
         <v>79</v>
       </c>
       <c r="Q19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R19" t="s">
         <v>79</v>
@@ -3623,10 +3626,10 @@
         <v>79</v>
       </c>
       <c r="U19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W19" t="s">
         <v>79</v>
@@ -3638,13 +3641,13 @@
         <v>79</v>
       </c>
       <c r="Z19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="s">
         <v>79</v>
       </c>
       <c r="AB19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC19" t="s">
         <v>79</v>
@@ -3653,7 +3656,7 @@
         <v>79</v>
       </c>
       <c r="AE19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF19" t="s">
         <v>79</v>
@@ -3677,25 +3680,25 @@
         <v>79</v>
       </c>
       <c r="AM19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AO19" t="s">
         <v>79</v>
       </c>
       <c r="AP19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AR19" t="s">
         <v>79</v>
       </c>
       <c r="AS19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT19" t="s">
         <v>79</v>
@@ -3707,19 +3710,19 @@
         <v>79</v>
       </c>
       <c r="AW19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AY19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AZ19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3727,160 +3730,160 @@
         <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV20" t="s">
         <v>79</v>
       </c>
       <c r="AW20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3888,7 +3891,7 @@
         <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
         <v>79</v>
@@ -3897,67 +3900,67 @@
         <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
         <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>79</v>
       </c>
       <c r="I21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z21" t="s">
         <v>79</v>
@@ -3966,19 +3969,19 @@
         <v>79</v>
       </c>
       <c r="AB21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG21" t="s">
         <v>79</v>
@@ -3993,22 +3996,22 @@
         <v>79</v>
       </c>
       <c r="AK21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="s">
         <v>79</v>
       </c>
       <c r="AN21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="s">
         <v>79</v>
       </c>
       <c r="AP21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ21" t="s">
         <v>79</v>
@@ -4029,19 +4032,19 @@
         <v>79</v>
       </c>
       <c r="AW21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX21" t="s">
         <v>79</v>
       </c>
       <c r="AY21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4049,28 +4052,28 @@
         <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J22" t="s">
         <v>79</v>
@@ -4091,7 +4094,7 @@
         <v>79</v>
       </c>
       <c r="P22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q22" t="s">
         <v>79</v>
@@ -4112,7 +4115,7 @@
         <v>79</v>
       </c>
       <c r="W22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X22" t="s">
         <v>79</v>
@@ -4136,73 +4139,73 @@
         <v>79</v>
       </c>
       <c r="AE22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL22" t="s">
         <v>81</v>
       </c>
-      <c r="AF22" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL22" t="s">
-        <v>80</v>
-      </c>
       <c r="AM22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AN22" t="s">
         <v>79</v>
       </c>
       <c r="AO22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AP22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AQ22" t="s">
         <v>79</v>
       </c>
       <c r="AR22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS22" t="s">
         <v>79</v>
       </c>
       <c r="AT22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AU22" t="s">
         <v>79</v>
       </c>
       <c r="AV22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AW22" t="s">
         <v>79</v>
       </c>
       <c r="AX22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AZ22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="BA22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:53">
@@ -4210,25 +4213,25 @@
         <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s">
         <v>79</v>
       </c>
       <c r="H23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s">
         <v>79</v>
@@ -4237,7 +4240,7 @@
         <v>79</v>
       </c>
       <c r="K23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L23" t="s">
         <v>79</v>
@@ -4249,7 +4252,7 @@
         <v>79</v>
       </c>
       <c r="O23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P23" t="s">
         <v>79</v>
@@ -4282,7 +4285,7 @@
         <v>79</v>
       </c>
       <c r="Z23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA23" t="s">
         <v>79</v>
@@ -4303,7 +4306,7 @@
         <v>79</v>
       </c>
       <c r="AG23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s">
         <v>79</v>
@@ -4312,7 +4315,7 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK23" t="s">
         <v>79</v>
@@ -4333,7 +4336,7 @@
         <v>79</v>
       </c>
       <c r="AQ23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR23" t="s">
         <v>79</v>
@@ -4357,13 +4360,13 @@
         <v>79</v>
       </c>
       <c r="AY23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:53">
@@ -4371,19 +4374,19 @@
         <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
         <v>79</v>
@@ -4404,7 +4407,7 @@
         <v>79</v>
       </c>
       <c r="M24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N24" t="s">
         <v>79</v>
@@ -4422,13 +4425,13 @@
         <v>79</v>
       </c>
       <c r="S24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T24" t="s">
         <v>79</v>
       </c>
       <c r="U24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V24" t="s">
         <v>79</v>
@@ -4440,25 +4443,25 @@
         <v>79</v>
       </c>
       <c r="Y24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF24" t="s">
         <v>79</v>
@@ -4503,7 +4506,7 @@
         <v>79</v>
       </c>
       <c r="AT24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU24" t="s">
         <v>79</v>
@@ -4512,19 +4515,19 @@
         <v>79</v>
       </c>
       <c r="AW24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:53">
@@ -4532,106 +4535,106 @@
         <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="s">
         <v>79</v>
@@ -4640,16 +4643,16 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP25" t="s">
         <v>79</v>
@@ -4667,25 +4670,25 @@
         <v>79</v>
       </c>
       <c r="AU25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:53">
@@ -4723,7 +4726,7 @@
         <v>79</v>
       </c>
       <c r="L26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M26" t="s">
         <v>79</v>
@@ -4741,7 +4744,7 @@
         <v>79</v>
       </c>
       <c r="R26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S26" t="s">
         <v>79</v>
@@ -4756,28 +4759,28 @@
         <v>79</v>
       </c>
       <c r="W26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X26" t="s">
         <v>79</v>
       </c>
       <c r="Y26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z26" t="s">
         <v>79</v>
       </c>
       <c r="AA26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AC26" t="s">
         <v>79</v>
       </c>
       <c r="AD26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE26" t="s">
         <v>79</v>
@@ -4789,7 +4792,7 @@
         <v>79</v>
       </c>
       <c r="AH26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s">
         <v>79</v>
@@ -4801,7 +4804,7 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="s">
         <v>79</v>
@@ -4825,28 +4828,28 @@
         <v>79</v>
       </c>
       <c r="AT26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU26" t="s">
         <v>79</v>
       </c>
       <c r="AV26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX26" t="s">
         <v>79</v>
       </c>
       <c r="AY26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AZ26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:53">
@@ -4881,13 +4884,13 @@
         <v>79</v>
       </c>
       <c r="K27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L27" t="s">
         <v>79</v>
       </c>
       <c r="M27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N27" t="s">
         <v>79</v>
@@ -4902,7 +4905,7 @@
         <v>79</v>
       </c>
       <c r="R27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S27" t="s">
         <v>79</v>
@@ -4917,7 +4920,7 @@
         <v>79</v>
       </c>
       <c r="W27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X27" t="s">
         <v>79</v>
@@ -4938,7 +4941,7 @@
         <v>79</v>
       </c>
       <c r="AD27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE27" t="s">
         <v>79</v>
@@ -4965,16 +4968,16 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AN27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ27" t="s">
         <v>79</v>
@@ -4983,16 +4986,16 @@
         <v>79</v>
       </c>
       <c r="AS27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AU27" t="s">
         <v>79</v>
       </c>
       <c r="AV27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW27" t="s">
         <v>79</v>
@@ -5001,13 +5004,13 @@
         <v>79</v>
       </c>
       <c r="AY27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AZ27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Wage_(non-qualified_labour,_agricultural)_tukey_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_agricultural)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="82">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -259,31 +259,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>14%</t>
   </si>
 </sst>
 </file>
@@ -853,7 +829,7 @@
         <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J2" t="s">
         <v>80</v>
@@ -880,7 +856,7 @@
         <v>79</v>
       </c>
       <c r="R2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S2" t="s">
         <v>79</v>
@@ -892,7 +868,7 @@
         <v>80</v>
       </c>
       <c r="V2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W2" t="s">
         <v>79</v>
@@ -979,13 +955,13 @@
         <v>80</v>
       </c>
       <c r="AY2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -1041,22 +1017,22 @@
         <v>80</v>
       </c>
       <c r="R3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S3" t="s">
         <v>80</v>
       </c>
       <c r="T3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U3" t="s">
         <v>80</v>
       </c>
       <c r="V3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X3" t="s">
         <v>80</v>
@@ -1071,7 +1047,7 @@
         <v>80</v>
       </c>
       <c r="AB3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC3" t="s">
         <v>80</v>
@@ -1140,13 +1116,13 @@
         <v>80</v>
       </c>
       <c r="AY3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1301,13 +1277,13 @@
         <v>79</v>
       </c>
       <c r="AY4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1435,7 +1411,7 @@
         <v>79</v>
       </c>
       <c r="AP5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ5" t="s">
         <v>79</v>
@@ -1462,13 +1438,13 @@
         <v>79</v>
       </c>
       <c r="AY5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1539,7 +1515,7 @@
         <v>80</v>
       </c>
       <c r="W6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X6" t="s">
         <v>80</v>
@@ -1557,10 +1533,10 @@
         <v>80</v>
       </c>
       <c r="AC6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE6" t="s">
         <v>79</v>
@@ -1578,7 +1554,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="s">
         <v>79</v>
@@ -1599,7 +1575,7 @@
         <v>80</v>
       </c>
       <c r="AQ6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AR6" t="s">
         <v>79</v>
@@ -1608,7 +1584,7 @@
         <v>80</v>
       </c>
       <c r="AT6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU6" t="s">
         <v>80</v>
@@ -1623,13 +1599,13 @@
         <v>79</v>
       </c>
       <c r="AY6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BA6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1754,10 +1730,10 @@
         <v>80</v>
       </c>
       <c r="AO7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ7" t="s">
         <v>80</v>
@@ -1784,13 +1760,13 @@
         <v>80</v>
       </c>
       <c r="AY7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1855,13 +1831,13 @@
         <v>79</v>
       </c>
       <c r="U8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V8" t="s">
         <v>80</v>
       </c>
       <c r="W8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X8" t="s">
         <v>79</v>
@@ -1873,13 +1849,13 @@
         <v>80</v>
       </c>
       <c r="AA8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD8" t="s">
         <v>80</v>
@@ -1894,7 +1870,7 @@
         <v>80</v>
       </c>
       <c r="AH8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s">
         <v>80</v>
@@ -1903,10 +1879,10 @@
         <v>79</v>
       </c>
       <c r="AK8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="s">
         <v>80</v>
@@ -1918,7 +1894,7 @@
         <v>80</v>
       </c>
       <c r="AP8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ8" t="s">
         <v>79</v>
@@ -1945,13 +1921,13 @@
         <v>80</v>
       </c>
       <c r="AY8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -2004,10 +1980,10 @@
         <v>80</v>
       </c>
       <c r="Q9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S9" t="s">
         <v>79</v>
@@ -2019,19 +1995,19 @@
         <v>79</v>
       </c>
       <c r="V9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W9" t="s">
         <v>80</v>
       </c>
       <c r="X9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="s">
         <v>80</v>
@@ -2040,10 +2016,10 @@
         <v>79</v>
       </c>
       <c r="AC9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE9" t="s">
         <v>79</v>
@@ -2055,13 +2031,13 @@
         <v>79</v>
       </c>
       <c r="AH9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK9" t="s">
         <v>80</v>
@@ -2070,7 +2046,7 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s">
         <v>79</v>
@@ -2106,13 +2082,13 @@
         <v>80</v>
       </c>
       <c r="AY9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2171,19 +2147,19 @@
         <v>80</v>
       </c>
       <c r="S10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U10" t="s">
         <v>80</v>
       </c>
       <c r="V10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X10" t="s">
         <v>80</v>
@@ -2195,10 +2171,10 @@
         <v>80</v>
       </c>
       <c r="AA10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC10" t="s">
         <v>80</v>
@@ -2267,13 +2243,13 @@
         <v>80</v>
       </c>
       <c r="AY10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2398,13 +2374,13 @@
         <v>80</v>
       </c>
       <c r="AO11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR11" t="s">
         <v>80</v>
@@ -2428,13 +2404,13 @@
         <v>80</v>
       </c>
       <c r="AY11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2559,7 +2535,7 @@
         <v>80</v>
       </c>
       <c r="AO12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP12" t="s">
         <v>80</v>
@@ -2574,28 +2550,28 @@
         <v>80</v>
       </c>
       <c r="AT12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU12" t="s">
         <v>80</v>
       </c>
       <c r="AV12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX12" t="s">
         <v>80</v>
       </c>
       <c r="AY12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2711,19 +2687,19 @@
         <v>80</v>
       </c>
       <c r="AL13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="s">
         <v>80</v>
       </c>
       <c r="AN13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ13" t="s">
         <v>79</v>
@@ -2738,10 +2714,10 @@
         <v>80</v>
       </c>
       <c r="AU13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW13" t="s">
         <v>80</v>
@@ -2750,13 +2726,13 @@
         <v>80</v>
       </c>
       <c r="AY13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2815,7 +2791,7 @@
         <v>80</v>
       </c>
       <c r="S14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T14" t="s">
         <v>79</v>
@@ -2824,10 +2800,10 @@
         <v>79</v>
       </c>
       <c r="V14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X14" t="s">
         <v>79</v>
@@ -2884,7 +2860,7 @@
         <v>79</v>
       </c>
       <c r="AP14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ14" t="s">
         <v>80</v>
@@ -2905,19 +2881,19 @@
         <v>79</v>
       </c>
       <c r="AW14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX14" t="s">
         <v>80</v>
       </c>
       <c r="AY14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -3030,16 +3006,16 @@
         <v>80</v>
       </c>
       <c r="AK15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO15" t="s">
         <v>80</v>
@@ -3048,13 +3024,13 @@
         <v>80</v>
       </c>
       <c r="AQ15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT15" t="s">
         <v>80</v>
@@ -3072,13 +3048,13 @@
         <v>80</v>
       </c>
       <c r="AY15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3197,49 +3173,49 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS16" t="s">
         <v>80</v>
       </c>
       <c r="AT16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3358,34 +3334,34 @@
         <v>79</v>
       </c>
       <c r="AM17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AN17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AO17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AP17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AR17" t="s">
         <v>79</v>
       </c>
       <c r="AS17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AT17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AU17" t="s">
         <v>80</v>
       </c>
       <c r="AV17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AW17" t="s">
         <v>79</v>
@@ -3394,13 +3370,13 @@
         <v>80</v>
       </c>
       <c r="AY17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AZ17" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="BA17" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3477,7 +3453,7 @@
         <v>80</v>
       </c>
       <c r="Y18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z18" t="s">
         <v>80</v>
@@ -3501,16 +3477,16 @@
         <v>79</v>
       </c>
       <c r="AG18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s">
         <v>79</v>
       </c>
       <c r="AI18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK18" t="s">
         <v>80</v>
@@ -3519,7 +3495,7 @@
         <v>79</v>
       </c>
       <c r="AM18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="s">
         <v>80</v>
@@ -3531,7 +3507,7 @@
         <v>80</v>
       </c>
       <c r="AQ18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AR18" t="s">
         <v>80</v>
@@ -3555,13 +3531,13 @@
         <v>80</v>
       </c>
       <c r="AY18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AZ18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3662,7 +3638,7 @@
         <v>79</v>
       </c>
       <c r="AG19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s">
         <v>79</v>
@@ -3683,7 +3659,7 @@
         <v>80</v>
       </c>
       <c r="AN19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AO19" t="s">
         <v>79</v>
@@ -3692,7 +3668,7 @@
         <v>80</v>
       </c>
       <c r="AQ19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AR19" t="s">
         <v>79</v>
@@ -3713,16 +3689,16 @@
         <v>80</v>
       </c>
       <c r="AX19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AY19" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AZ19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA19" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3868,7 +3844,7 @@
         <v>80</v>
       </c>
       <c r="AV20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW20" t="s">
         <v>80</v>
@@ -3877,13 +3853,13 @@
         <v>80</v>
       </c>
       <c r="AY20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3897,13 +3873,13 @@
         <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
         <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s">
         <v>80</v>
@@ -4008,13 +3984,13 @@
         <v>80</v>
       </c>
       <c r="AO21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="s">
         <v>80</v>
       </c>
       <c r="AQ21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR21" t="s">
         <v>79</v>
@@ -4038,13 +4014,13 @@
         <v>79</v>
       </c>
       <c r="AY21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4139,7 +4115,7 @@
         <v>79</v>
       </c>
       <c r="AE22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AF22" t="s">
         <v>79</v>
@@ -4160,19 +4136,19 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AM22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AN22" t="s">
         <v>79</v>
       </c>
       <c r="AO22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AP22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AQ22" t="s">
         <v>79</v>
@@ -4184,13 +4160,13 @@
         <v>79</v>
       </c>
       <c r="AT22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AU22" t="s">
         <v>79</v>
       </c>
       <c r="AV22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AW22" t="s">
         <v>79</v>
@@ -4199,13 +4175,13 @@
         <v>80</v>
       </c>
       <c r="AY22" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AZ22" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BA22" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:53">
@@ -4360,13 +4336,13 @@
         <v>79</v>
       </c>
       <c r="AY23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:53">
@@ -4479,7 +4455,7 @@
         <v>79</v>
       </c>
       <c r="AK24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL24" t="s">
         <v>79</v>
@@ -4521,13 +4497,13 @@
         <v>80</v>
       </c>
       <c r="AY24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:53">
@@ -4637,10 +4613,10 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="s">
         <v>80</v>
@@ -4655,19 +4631,19 @@
         <v>80</v>
       </c>
       <c r="AP25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU25" t="s">
         <v>80</v>
@@ -4682,13 +4658,13 @@
         <v>80</v>
       </c>
       <c r="AY25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:53">
@@ -4771,10 +4747,10 @@
         <v>79</v>
       </c>
       <c r="AA26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AB26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AC26" t="s">
         <v>79</v>
@@ -4843,13 +4819,13 @@
         <v>79</v>
       </c>
       <c r="AY26" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AZ26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA26" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:53">
@@ -4869,7 +4845,7 @@
         <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s">
         <v>79</v>
@@ -4968,13 +4944,13 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AN27" t="s">
         <v>80</v>
       </c>
       <c r="AO27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AP27" t="s">
         <v>80</v>
@@ -4989,7 +4965,7 @@
         <v>80</v>
       </c>
       <c r="AT27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AU27" t="s">
         <v>79</v>
@@ -5004,13 +4980,13 @@
         <v>79</v>
       </c>
       <c r="AY27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AZ27" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="BA27" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Wage_(non-qualified_labour,_agricultural)_tukey_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_agricultural)_tukey_classification_matrix.xlsx
@@ -253,7 +253,7 @@
     <t>Yambio</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
